--- a/i_test/test_D3_selezione_coorte/D3_ASL.xlsx
+++ b/i_test/test_D3_selezione_coorte/D3_ASL.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t xml:space="preserve">person_id</t>
   </si>
@@ -43,10 +43,13 @@
     <t xml:space="preserve">P07</t>
   </si>
   <si>
+    <t xml:space="preserve">P08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SE</t>
+  </si>
+  <si>
     <t xml:space="preserve">P09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE</t>
   </si>
   <si>
     <t xml:space="preserve">P10</t>
@@ -166,7 +169,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -219,7 +222,7 @@
         <v>19950101</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>20151231</v>
+        <v>20251231</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>8</v>
@@ -227,16 +230,16 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>20160101</v>
+        <v>19950101</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>20251231</v>
+        <v>20151231</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -244,13 +247,13 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>19950101</v>
+        <v>20160101</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>20251231</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -264,21 +267,21 @@
         <v>20251231</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>19950101</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>20251231</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>19950101</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>20251231</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -292,7 +295,7 @@
         <v>20251231</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -306,6 +309,20 @@
         <v>20251231</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>19950101</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>20251231</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>5</v>
       </c>
     </row>
